--- a/docs/Cadrage projet/perturbation J3/equipe-13-product-backlog-v1.2.xlsx
+++ b/docs/Cadrage projet/perturbation J3/equipe-13-product-backlog-v1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjetApo\IPSSI_APOCAL_KIT_13\docs\Cadrage projet\perturbation J3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F5AAFE2-55A2-4B85-BC1F-7E03CBEA1E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904C58AC-2653-4DFF-8E05-CF37FC851C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="245">
   <si>
     <t>IDENTIFICATION DU DOCUMENT</t>
   </si>
@@ -3479,7 +3479,9 @@
       </c>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
+      <c r="J43" s="20" t="s">
+        <v>99</v>
+      </c>
       <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11" ht="69" thickBot="1" x14ac:dyDescent="0.35">
